--- a/artfynd/A 1684-2023 artfynd.xlsx
+++ b/artfynd/A 1684-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1684-2023 artfynd.xlsx
+++ b/artfynd/A 1684-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3688,6 +3688,121 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126293041</v>
+      </c>
+      <c r="B28" t="n">
+        <v>56948</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sandhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>718532</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6395967</v>
+      </c>
+      <c r="S28" t="n">
+        <v>130</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>David Armini</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>David Armini</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1684-2023 artfynd.xlsx
+++ b/artfynd/A 1684-2023 artfynd.xlsx
@@ -3693,7 +3693,7 @@
         <v>126293041</v>
       </c>
       <c r="B28" t="n">
-        <v>56948</v>
+        <v>56952</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 1684-2023 artfynd.xlsx
+++ b/artfynd/A 1684-2023 artfynd.xlsx
@@ -3693,7 +3693,7 @@
         <v>126293041</v>
       </c>
       <c r="B28" t="n">
-        <v>56952</v>
+        <v>56953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
